--- a/gpt_5_mini_results.xlsx
+++ b/gpt_5_mini_results.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="17">
   <si>
     <t>Gitlab</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>skill调用次数统计</t>
+  </si>
+  <si>
+    <t>skill成功率</t>
   </si>
 </sst>
 </file>
@@ -1476,10 +1479,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:AE22"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="23" width="11.4711538461538" customWidth="1"/>
+    <col min="1" max="31" width="12.0192307692308" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.8" spans="1:1">
@@ -1487,7 +1490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="17.55" spans="1:23">
+    <row r="2" ht="17.55" spans="1:31">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1551,8 +1554,29 @@
       <c r="W2" s="12" t="s">
         <v>7</v>
       </c>
+      <c r="Y2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE2" s="12" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" ht="17.55" spans="1:23">
+    <row r="3" ht="17.55" spans="1:31">
       <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1604,8 +1628,17 @@
       <c r="U3" s="17"/>
       <c r="V3" s="17"/>
       <c r="W3" s="21"/>
+      <c r="Y3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z3" s="17"/>
+      <c r="AA3" s="17"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="17"/>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="21"/>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:31">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
@@ -1669,8 +1702,17 @@
       <c r="W4" s="22">
         <v>0.012</v>
       </c>
+      <c r="Y4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="18"/>
+      <c r="AA4" s="18"/>
+      <c r="AB4" s="18"/>
+      <c r="AC4" s="18"/>
+      <c r="AD4" s="18"/>
+      <c r="AE4" s="22"/>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:31">
       <c r="A5" s="8" t="s">
         <v>10</v>
       </c>
@@ -1734,8 +1776,17 @@
       <c r="W5" s="23">
         <v>2.722</v>
       </c>
+      <c r="Y5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z5" s="19"/>
+      <c r="AA5" s="19"/>
+      <c r="AB5" s="19"/>
+      <c r="AC5" s="19"/>
+      <c r="AD5" s="19"/>
+      <c r="AE5" s="23"/>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:31">
       <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
@@ -1799,13 +1850,22 @@
       <c r="W6" s="24">
         <v>0.166</v>
       </c>
+      <c r="Y6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="24"/>
     </row>
     <row r="8" ht="28.8" spans="1:1">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="17.55" spans="1:23">
+    <row r="9" ht="17.55" spans="1:31">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
@@ -1869,8 +1929,29 @@
       <c r="W9" s="12" t="s">
         <v>7</v>
       </c>
+      <c r="Y9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE9" s="12" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="10" ht="17.55" spans="1:23">
+    <row r="10" ht="17.55" spans="1:31">
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
@@ -1922,8 +2003,17 @@
       <c r="U10" s="17"/>
       <c r="V10" s="17"/>
       <c r="W10" s="21"/>
+      <c r="Y10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17"/>
+      <c r="AB10" s="17"/>
+      <c r="AC10" s="17"/>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="21"/>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:31">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
@@ -1987,8 +2077,17 @@
       <c r="W11" s="22">
         <v>0.018</v>
       </c>
+      <c r="Y11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z11" s="18"/>
+      <c r="AA11" s="18"/>
+      <c r="AB11" s="18"/>
+      <c r="AC11" s="18"/>
+      <c r="AD11" s="18"/>
+      <c r="AE11" s="22"/>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:31">
       <c r="A12" s="8" t="s">
         <v>10</v>
       </c>
@@ -2052,8 +2151,17 @@
       <c r="W12" s="23">
         <v>3.674</v>
       </c>
+      <c r="Y12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
+      <c r="AC12" s="19"/>
+      <c r="AD12" s="19"/>
+      <c r="AE12" s="23"/>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:31">
       <c r="A13" s="10" t="s">
         <v>11</v>
       </c>
@@ -2117,13 +2225,22 @@
       <c r="W13" s="24">
         <v>0.482</v>
       </c>
+      <c r="Y13" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AD13" s="20"/>
+      <c r="AE13" s="24"/>
     </row>
     <row r="15" ht="28.8" spans="1:1">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" ht="17.55" spans="1:23">
+    <row r="16" ht="17.55" spans="1:31">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
@@ -2187,8 +2304,29 @@
       <c r="W16" s="12" t="s">
         <v>7</v>
       </c>
+      <c r="Y16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA16" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE16" s="12" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="17" ht="17.55" spans="1:23">
+    <row r="17" ht="17.55" spans="1:31">
       <c r="A17" s="4" t="s">
         <v>8</v>
       </c>
@@ -2240,8 +2378,17 @@
       <c r="U17" s="17"/>
       <c r="V17" s="17"/>
       <c r="W17" s="21"/>
+      <c r="Y17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z17" s="17"/>
+      <c r="AA17" s="17"/>
+      <c r="AB17" s="17"/>
+      <c r="AC17" s="17"/>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="21"/>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:31">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
@@ -2305,8 +2452,17 @@
       <c r="W18" s="22">
         <v>0.025</v>
       </c>
+      <c r="Y18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z18" s="18"/>
+      <c r="AA18" s="18"/>
+      <c r="AB18" s="18"/>
+      <c r="AC18" s="18"/>
+      <c r="AD18" s="18"/>
+      <c r="AE18" s="22"/>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:31">
       <c r="A19" s="8" t="s">
         <v>10</v>
       </c>
@@ -2358,8 +2514,17 @@
       <c r="U19" s="19"/>
       <c r="V19" s="19"/>
       <c r="W19" s="23"/>
+      <c r="Y19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z19" s="19"/>
+      <c r="AA19" s="19"/>
+      <c r="AB19" s="19"/>
+      <c r="AC19" s="19"/>
+      <c r="AD19" s="19"/>
+      <c r="AE19" s="23"/>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:31">
       <c r="A20" s="10" t="s">
         <v>11</v>
       </c>
@@ -2411,13 +2576,25 @@
       <c r="U20" s="20"/>
       <c r="V20" s="20"/>
       <c r="W20" s="24"/>
+      <c r="Y20" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z20" s="20"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="20"/>
+      <c r="AD20" s="20"/>
+      <c r="AE20" s="24"/>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
         <v>14</v>
       </c>
       <c r="C22" t="s">
         <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
